--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487788_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487788_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0345</v>
+        <v>8.3093</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4828</v>
+        <v>6.4053</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5517</v>
+        <v>1.904</v>
       </c>
       <c r="G2" t="n">
         <v>5.9271</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1039</v>
+        <v>0.171</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6277</v>
+        <v>0.2948</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4762</v>
+        <v>-0.1239</v>
       </c>
       <c r="V2" t="n">
         <v>2.2112</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5796</v>
+        <v>7.4793</v>
       </c>
       <c r="E3" t="n">
-        <v>4.139</v>
+        <v>5.1267</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4406</v>
+        <v>2.3525</v>
       </c>
       <c r="G3" t="n">
         <v>4.1866</v>
@@ -688,13 +688,13 @@
         <v>2.9137</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.043</v>
+        <v>0.8566</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.109</v>
+        <v>0.8787</v>
       </c>
       <c r="U3" t="n">
-        <v>0.066</v>
+        <v>-0.0221</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4776</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7813</v>
+        <v>5.0268</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5918</v>
+        <v>2.5142</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1896</v>
+        <v>2.5125</v>
       </c>
       <c r="G4" t="n">
         <v>3.1324</v>
@@ -766,13 +766,13 @@
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3968</v>
+        <v>-0.1513</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9786</v>
+        <v>-0.0562</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4181</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>3.5026</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2304</v>
+        <v>1.8398</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8797</v>
+        <v>2.1673</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6492</v>
+        <v>-0.3275</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0132</v>
+        <v>1.7855</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0323</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.019</v>
+        <v>1.7088</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0786</v>
+        <v>3.1817</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9956</v>
+        <v>0.5137</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.917</v>
+        <v>2.668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9347</v>
+        <v>-1.3962</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0367</v>
+        <v>-0.4369</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.102</v>
+        <v>-0.9593</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8731</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5554</v>
+        <v>0.0543</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6336</v>
+        <v>0.0262</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.0281</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.2112</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.3787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0039</v>
+        <v>1.5162</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5663</v>
+        <v>2.1948</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5624</v>
+        <v>-0.6786</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7855</v>
+        <v>1.0132</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07679999999999999</v>
+        <v>3.0323</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7088</v>
+        <v>-2.019</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1817</v>
+        <v>0.0786</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5137</v>
+        <v>1.9956</v>
       </c>
       <c r="L6" t="n">
-        <v>2.668</v>
+        <v>-1.917</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3962</v>
+        <v>0.9347</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4369</v>
+        <v>1.0367</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9593</v>
+        <v>-0.102</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8731</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7816</v>
+        <v>0.8411</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5748</v>
+        <v>0.9487</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2068</v>
+        <v>-0.1076</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.2112</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.3787</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9245</v>
+        <v>0.6896</v>
       </c>
       <c r="E7" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9897</v>
+        <v>0.7548</v>
       </c>
       <c r="G7" t="n">
         <v>0.2857</v>
@@ -1000,13 +1000,13 @@
         <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4306</v>
+        <v>0.1957</v>
       </c>
       <c r="T7" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4958</v>
+        <v>0.261</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7806</v>
+        <v>0.2116</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1342</v>
+        <v>0.4174</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9148</v>
+        <v>-0.2058</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7528</v>
+        <v>0.6691</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2214</v>
+        <v>0.1621</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4686</v>
+        <v>0.507</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9408</v>
+        <v>1.2732</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6665</v>
+        <v>0.0192</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2743</v>
+        <v>1.254</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.188</v>
+        <v>-0.6041</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.1429</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7429</v>
+        <v>-0.747</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.5786</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.2435</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>4.0841</v>
+        <v>0.1887</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6462</v>
+        <v>0.1848</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4379</v>
+        <v>0.0039</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4776</v>
+        <v>-0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0163</v>
+        <v>-0.3494</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3103</v>
+        <v>-0.4955</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2939</v>
+        <v>0.1461</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6691</v>
+        <v>-0.4022</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1621</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.507</v>
+        <v>0.4058</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2732</v>
+        <v>-0.0388</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0192</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.254</v>
+        <v>0.618</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6041</v>
+        <v>-0.3634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1429</v>
+        <v>-0.1512</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.747</v>
+        <v>-0.2123</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0065</v>
+        <v>-0.1553</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0776</v>
+        <v>-0.4567</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0842</v>
+        <v>0.3014</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1145</v>
+        <v>-1.0846</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4955</v>
+        <v>-1.5693</v>
       </c>
       <c r="F10" t="n">
-        <v>0.381</v>
+        <v>0.4847</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4022</v>
+        <v>-1.5194</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.823</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4058</v>
+        <v>-0.6964</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0388</v>
+        <v>-0.5192</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.676</v>
       </c>
       <c r="L10" t="n">
-        <v>0.618</v>
+        <v>0.1568</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3634</v>
+        <v>-1.0002</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1512</v>
+        <v>-0.147</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2123</v>
+        <v>-0.8532</v>
       </c>
       <c r="P10" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0796</v>
+        <v>0.2267</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4567</v>
+        <v>-0.0095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5363</v>
+        <v>0.2362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8181</v>
+        <v>-1.7083</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4203</v>
+        <v>-3.212</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6022</v>
+        <v>1.5038</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5194</v>
+        <v>1.7528</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.823</v>
+        <v>2.2214</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6964</v>
+        <v>-0.4686</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5192</v>
+        <v>1.9408</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.676</v>
+        <v>1.6665</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1568</v>
+        <v>0.2743</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0002</v>
+        <v>-0.188</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.147</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8532</v>
+        <v>-0.7429</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2081</v>
+        <v>-4.5786</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>-6.2435</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4932</v>
+        <v>1.5952</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1396</v>
+        <v>1.5683</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3536</v>
+        <v>0.0268</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5089</v>
+        <v>-3.2309</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0272</v>
+        <v>-2.1986</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5361</v>
+        <v>-1.0322</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2938</v>
+        <v>-4.025</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4797</v>
+        <v>-0.7569</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8141</v>
+        <v>-3.2681</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4323</v>
+        <v>-2.3554</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0428</v>
+        <v>-0.369</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3896</v>
+        <v>-1.9864</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-1.6697</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4369</v>
+        <v>-0.3879</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4245</v>
+        <v>-1.2818</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6413</v>
+        <v>0.0054</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6458</v>
+        <v>0.1567</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0045</v>
+        <v>-0.1513</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6889</v>
+        <v>-0.4599</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5026</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8026</v>
+        <v>-3.9398</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7997</v>
+        <v>-0.5505</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0029</v>
+        <v>-3.3893</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.025</v>
+        <v>-2.2938</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7569</v>
+        <v>-0.4797</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2681</v>
+        <v>-1.8141</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3554</v>
+        <v>-1.4323</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.369</v>
+        <v>-0.0428</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9864</v>
+        <v>-1.3896</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6697</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3879</v>
+        <v>-0.4369</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2818</v>
+        <v>-0.4245</v>
       </c>
       <c r="P13" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5663</v>
+        <v>0.2104</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4443</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.122</v>
+        <v>0.1423</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4599</v>
+        <v>-2.6889</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4599</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.107</v>
+        <v>14.7596</v>
       </c>
       <c r="E14" t="n">
-        <v>10.0822</v>
+        <v>10.7346</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0251</v>
+        <v>4.025</v>
       </c>
       <c r="G14" t="n">
         <v>10.512</v>
@@ -1516,13 +1516,13 @@
         <v>10.5121</v>
       </c>
       <c r="I14" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="J14" t="n">
         <v>15.0242</v>
       </c>
       <c r="K14" t="n">
-        <v>8.472600000000002</v>
+        <v>8.4726</v>
       </c>
       <c r="L14" t="n">
         <v>6.551500000000001</v>
@@ -1546,10 +1546,10 @@
         <v>15.6089</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3861</v>
+        <v>4.0385</v>
       </c>
       <c r="T14" t="n">
-        <v>2.886499999999999</v>
+        <v>3.5387</v>
       </c>
       <c r="U14" t="n">
         <v>0.4996</v>
@@ -1558,7 +1558,7 @@
         <v>-0.8313999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>6.7398</v>
+        <v>6.739800000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-7.5712</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.587</v>
+        <v>4.1798</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7279</v>
+        <v>4.442</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1409</v>
+        <v>-0.2623</v>
       </c>
       <c r="G15" t="n">
         <v>3.6393</v>
@@ -1624,13 +1624,13 @@
         <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6688</v>
+        <v>0.2616</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7203</v>
+        <v>0.4344</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0515</v>
+        <v>-0.1728</v>
       </c>
       <c r="V15" t="n">
         <v>0.0708</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.602</v>
+        <v>1.6084</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1078</v>
+        <v>2.0006</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5058</v>
+        <v>-0.3923</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4001</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8377</v>
+        <v>0.844</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3849</v>
+        <v>0.2777</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4528</v>
+        <v>0.5663</v>
       </c>
       <c r="V16" t="n">
         <v>0.1238</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5567</v>
+        <v>1.1972</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2626</v>
+        <v>2.5841</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7059</v>
+        <v>-1.3869</v>
       </c>
       <c r="G17" t="n">
         <v>1.5116</v>
@@ -1780,13 +1780,13 @@
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6656</v>
+        <v>-1.0251</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.5672</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.777</v>
+        <v>-0.4579</v>
       </c>
       <c r="V17" t="n">
         <v>1.7513</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5104</v>
+        <v>0.9263</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8069</v>
+        <v>1.0212</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2965</v>
+        <v>-0.0949</v>
       </c>
       <c r="G18" t="n">
         <v>1.0209</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7405</v>
+        <v>-0.3246</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3138</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4266</v>
+        <v>-0.225</v>
       </c>
       <c r="V18" t="n">
         <v>0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0214</v>
+        <v>0.1802</v>
       </c>
       <c r="E19" t="n">
         <v>-0.131</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1096</v>
+        <v>0.3112</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5723</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3523</v>
+        <v>-0.1507</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2486</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1037</v>
+        <v>0.0979</v>
       </c>
       <c r="V19" t="n">
         <v>0.0708</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2177</v>
+        <v>-0.6843</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5421</v>
+        <v>1.7564</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7597</v>
+        <v>-2.4407</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4553</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8331</v>
+        <v>-0.2998</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3014</v>
+        <v>-0.0871</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5317</v>
+        <v>-0.2127</v>
       </c>
       <c r="V20" t="n">
         <v>0.0708</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7329</v>
+        <v>-3.2226</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6353</v>
+        <v>-3.5281</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.3056</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6703</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0928</v>
+        <v>-0.5824</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1743</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9185</v>
+        <v>-0.5153</v>
       </c>
       <c r="V21" t="n">
         <v>0.0708</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3484</v>
+        <v>-3.2626</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0605</v>
+        <v>-2.5248</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2879</v>
+        <v>-0.7379</v>
       </c>
       <c r="G22" t="n">
         <v>-6.017</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3616</v>
+        <v>-0.2758</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6433</v>
+        <v>-0.1076</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7183</v>
+        <v>-0.1683</v>
       </c>
       <c r="V22" t="n">
         <v>2.4058</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7591</v>
+        <v>-5.8193</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8751</v>
+        <v>-5.5536</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1159</v>
+        <v>-0.2657</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7622</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4964</v>
+        <v>-0.5566</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4319</v>
+        <v>-0.1105</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0645</v>
+        <v>-0.4462</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2838</v>
+        <v>-7.7814</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0003</v>
+        <v>-4.3218</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2835</v>
+        <v>-3.4596</v>
       </c>
       <c r="G24" t="n">
         <v>-3.8067</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6498</v>
+        <v>0.1522</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3972</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2525</v>
+        <v>0.0764</v>
       </c>
       <c r="V24" t="n">
         <v>-3.5026</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.1072</v>
+        <v>-12.6783</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.254899999999999</v>
+        <v>-4.254999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.8523</v>
+        <v>-8.423500000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-10.5121</v>
@@ -2404,13 +2404,13 @@
         <v>14.5683</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.386</v>
+        <v>-1.9572</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4994999999999998</v>
+        <v>-0.4997000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.886499999999999</v>
+        <v>-1.4576</v>
       </c>
       <c r="V25" t="n">
         <v>0.8315999999999999</v>
